--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260914.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260914.xlsx
@@ -601,39 +601,39 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>華碩電腦</t>
+          <t>聯詠科技</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>6,323,000</t>
+          <t>10,700,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.93%</t>
+          <t>3.96%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>聯詠科技</t>
+          <t>華碩電腦</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>10,700,000</t>
+          <t>6,323,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -645,66 +645,66 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>202610WTX</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>115/10台股期貨</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>5,160,105,862</t>
+          <t>550</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.36%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>202610WTX</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>115/10台股期貨</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>22,333,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>22,333,000</t>
+          <t>6,331,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
@@ -748,95 +748,95 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>2.99%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>6,331,000</t>
+          <t>10,592,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>10,500,000</t>
+          <t>4,043,682,396</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>廣達電腦</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>21,691,000</t>
+          <t>11,980,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.65%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>廣達電腦</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>11,848,000</t>
+          <t>21,845,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.63%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
@@ -880,51 +880,51 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>568,000</t>
+          <t>6,897,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>6,897,000</t>
+          <t>4,101,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
@@ -946,46 +946,46 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>4,032,000</t>
+          <t>585,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>9,839,000</t>
+          <t>23,080,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,22 +997,22 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>23,080,000</t>
+          <t>9,933,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
@@ -1034,73 +1034,73 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.22%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>信邦電子</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>9,594,000</t>
+          <t>2,270,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.06%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>信邦電子</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>4,364,000</t>
+          <t>9,594,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>2,270,000</t>
+          <t>4,364,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
@@ -1166,117 +1166,117 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>14,684,000</t>
+          <t>15,578,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>15,578,000</t>
+          <t>5,324,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>5,324,000</t>
+          <t>14,684,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,633,551,204</t>
+          <t>42,169,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>42,169,000</t>
+          <t>2,581,961,204</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>6,686,000</t>
+          <t>6,795,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -1364,112 +1364,112 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>至上電子</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>26,620,004</t>
+          <t>7,991,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>至上電子</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>7,991,000</t>
+          <t>26,620,004</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>10,287,000</t>
+          <t>14,913,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>9,344,000</t>
+          <t>10,287,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>14,476,000</t>
+          <t>9,344,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1496,51 +1496,51 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>23,694,000</t>
+          <t>15,340,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>15,340,000</t>
+          <t>23,694,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>48,390,000</t>
+          <t>50,331,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1635,44 +1635,44 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>1,593,000</t>
+          <t>18,948,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>18,948,000</t>
+          <t>1,593,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-165,448,000</t>
+          <t>-128,648,250</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.09%</t>
         </is>
       </c>
     </row>
